--- a/mab/fuzzy_outputs/Final fuzzy in the 1st/output_2025-04-10_17-53-08.xlsx
+++ b/mab/fuzzy_outputs/Final fuzzy in the 1st/output_2025-04-10_17-53-08.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ognjen\axl_mab\Axelrod\mab\fuzzy_outputs\Final fuzzy in the 1st\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB9C7C0-F974-4FAB-AE9F-DB031DF9C7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rank_List" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,7 @@
     <sheet name="Cooperation_Matrix" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_Cooperation_Matrix" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -94,8 +100,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,13 +164,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +216,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -236,6 +250,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -270,9 +285,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -445,11 +461,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -475,7 +499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -495,16 +519,16 @@
         <v>0.74</v>
       </c>
       <c r="G2">
-        <v>0.7333333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="H2">
-        <v>0.3072058198207028</v>
+        <v>0.30720581982070277</v>
       </c>
       <c r="I2">
-        <v>0.3143896805306057</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>0.31438968053060568</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -521,19 +545,19 @@
         <v>2106</v>
       </c>
       <c r="F3">
-        <v>0.636</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="G3">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="H3">
-        <v>0.2840231720656843</v>
+        <v>0.28402317206568428</v>
       </c>
       <c r="I3">
-        <v>0.3276896089393754</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>0.32768960893937538</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -550,19 +574,19 @@
         <v>2766</v>
       </c>
       <c r="F4">
-        <v>0.8553333333333333</v>
+        <v>0.85533333333333328</v>
       </c>
       <c r="G4">
-        <v>0.9333333333333333</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="H4">
-        <v>0.3331808069127841</v>
+        <v>0.33318080691278412</v>
       </c>
       <c r="I4">
         <v>0.2941585298527567</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -579,19 +603,19 @@
         <v>2421</v>
       </c>
       <c r="F5">
-        <v>0.7403333333333333</v>
+        <v>0.74033333333333329</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0.3092149811641854</v>
+        <v>0.30921498116418539</v>
       </c>
       <c r="I5">
         <v>0.3108643745552026</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -614,13 +638,13 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0.363034601952077</v>
+        <v>0.36303460195207699</v>
       </c>
       <c r="I6">
-        <v>0.2665619843159506</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>0.26656198431595057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -637,19 +661,19 @@
         <v>2127</v>
       </c>
       <c r="F7">
-        <v>0.643</v>
+        <v>0.64300000000000002</v>
       </c>
       <c r="G7">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="H7">
-        <v>0.2904223522025414</v>
+        <v>0.29042235220254142</v>
       </c>
       <c r="I7">
-        <v>0.3480496256246701</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.34804962562467012</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -666,19 +690,19 @@
         <v>2086</v>
       </c>
       <c r="F8">
-        <v>0.6286666666666667</v>
+        <v>0.62866666666666671</v>
       </c>
       <c r="G8">
         <v>0.8</v>
       </c>
       <c r="H8">
-        <v>0.2846990948009573</v>
+        <v>0.28469909480095729</v>
       </c>
       <c r="I8">
-        <v>0.3373746074262963</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.33737460742629632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -695,19 +719,19 @@
         <v>1905</v>
       </c>
       <c r="F9">
-        <v>0.5683333333333334</v>
+        <v>0.56833333333333336</v>
       </c>
       <c r="G9">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H9">
-        <v>0.26976603402592</v>
+        <v>0.26976603402591998</v>
       </c>
       <c r="I9">
-        <v>0.3402681082845541</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.34026810828455412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -724,19 +748,19 @@
         <v>1930</v>
       </c>
       <c r="F10">
-        <v>0.5766666666666667</v>
+        <v>0.57666666666666666</v>
       </c>
       <c r="G10">
-        <v>0.7333333333333333</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="H10">
-        <v>0.2717751914822431</v>
+        <v>0.27177519148224311</v>
       </c>
       <c r="I10">
         <v>0.3388819267287459</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -753,19 +777,19 @@
         <v>1802</v>
       </c>
       <c r="F11">
-        <v>0.584</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="G11">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H11">
-        <v>0.2227911054615205</v>
+        <v>0.22279110546152051</v>
       </c>
       <c r="I11">
         <v>0.1071233833785482</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -782,7 +806,7 @@
         <v>1133</v>
       </c>
       <c r="F12">
-        <v>0.3776666666666667</v>
+        <v>0.37766666666666671</v>
       </c>
       <c r="G12">
         <v>0.6</v>
@@ -791,10 +815,10 @@
         <v>0.1111110849777196</v>
       </c>
       <c r="I12">
-        <v>-0.1752024645834371</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>-0.17520246458343711</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -811,19 +835,19 @@
         <v>950</v>
       </c>
       <c r="F13">
-        <v>0.3136666666666666</v>
+        <v>0.31366666666666659</v>
       </c>
       <c r="G13">
-        <v>0.2666666666666667</v>
+        <v>0.26666666666666672</v>
       </c>
       <c r="H13">
         <v>0.1158717778976406</v>
       </c>
       <c r="I13">
-        <v>-0.107784004445614</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>-0.10778400444561401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -840,19 +864,19 @@
         <v>1037</v>
       </c>
       <c r="F14">
-        <v>0.3406666666666667</v>
+        <v>0.34066666666666667</v>
       </c>
       <c r="G14">
         <v>0.2</v>
       </c>
       <c r="H14">
-        <v>0.1264737063248303</v>
+        <v>0.12647370632483029</v>
       </c>
       <c r="I14">
-        <v>-0.1130758467749391</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>-0.11307584677493911</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -869,19 +893,19 @@
         <v>1643</v>
       </c>
       <c r="F15">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="G15">
-        <v>0.6666666666666666</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H15">
-        <v>0.1871654769826883</v>
+        <v>0.18716547698268829</v>
       </c>
       <c r="I15">
-        <v>0.009050795603043634</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>9.0507956030436345E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -901,16 +925,16 @@
         <v>0.307</v>
       </c>
       <c r="G16">
-        <v>0.4666666666666667</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="H16">
         <v>0.1208522655849001</v>
       </c>
       <c r="I16">
-        <v>-0.08511020878624047</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>-8.5110208786240468E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -927,16 +951,16 @@
         <v>1585</v>
       </c>
       <c r="F17">
-        <v>0.494</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G17">
         <v>0.8</v>
       </c>
       <c r="H17">
-        <v>0.1829321103577347</v>
+        <v>0.18293211035773471</v>
       </c>
       <c r="I17">
-        <v>0.008568423420415019</v>
+        <v>8.5684234204150191E-3</v>
       </c>
     </row>
   </sheetData>
@@ -945,11 +969,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
@@ -999,7 +1023,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1007,7 +1031,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -1019,7 +1043,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="H2">
         <v>3</v>
@@ -1031,19 +1055,19 @@
         <v>2.625</v>
       </c>
       <c r="K2">
-        <v>2.985</v>
+        <v>2.9849999999999999</v>
       </c>
       <c r="L2">
         <v>1.355</v>
       </c>
       <c r="M2">
-        <v>1.255</v>
+        <v>1.2549999999999999</v>
       </c>
       <c r="N2">
-        <v>1.285</v>
+        <v>1.2849999999999999</v>
       </c>
       <c r="O2">
-        <v>2.295</v>
+        <v>2.2949999999999999</v>
       </c>
       <c r="P2">
         <v>2.31</v>
@@ -1052,7 +1076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1093,7 +1117,7 @@
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>1.465</v>
+        <v>1.4650000000000001</v>
       </c>
       <c r="O3">
         <v>2.6</v>
@@ -1105,7 +1129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -1134,19 +1158,19 @@
         <v>3</v>
       </c>
       <c r="J4">
-        <v>2.775</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="K4">
-        <v>0.075</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="L4">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="M4">
-        <v>2.685</v>
+        <v>2.6850000000000001</v>
       </c>
       <c r="N4">
-        <v>2.805</v>
+        <v>2.8050000000000002</v>
       </c>
       <c r="O4">
         <v>1.59</v>
@@ -1158,7 +1182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1187,22 +1211,22 @@
         <v>3</v>
       </c>
       <c r="J5">
-        <v>3.045</v>
+        <v>3.0449999999999999</v>
       </c>
       <c r="K5">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="L5">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="M5">
-        <v>2.615</v>
+        <v>2.6150000000000002</v>
       </c>
       <c r="N5">
         <v>2.145</v>
       </c>
       <c r="O5">
-        <v>2.135</v>
+        <v>2.1349999999999998</v>
       </c>
       <c r="P5">
         <v>2.09</v>
@@ -1211,7 +1235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1219,7 +1243,7 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1231,7 +1255,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -1240,16 +1264,16 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>2.905</v>
+        <v>2.9049999999999998</v>
       </c>
       <c r="K6">
-        <v>1.285</v>
+        <v>1.2849999999999999</v>
       </c>
       <c r="L6">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="M6">
-        <v>1.215</v>
+        <v>1.2150000000000001</v>
       </c>
       <c r="N6">
         <v>1.33</v>
@@ -1264,7 +1288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -1296,19 +1320,19 @@
         <v>2.63</v>
       </c>
       <c r="K7">
-        <v>2.525</v>
+        <v>2.5249999999999999</v>
       </c>
       <c r="L7">
-        <v>1.515</v>
+        <v>1.5149999999999999</v>
       </c>
       <c r="M7">
-        <v>1.245</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="N7">
-        <v>1.765</v>
+        <v>1.7649999999999999</v>
       </c>
       <c r="O7">
-        <v>2.945</v>
+        <v>2.9449999999999998</v>
       </c>
       <c r="P7">
         <v>2.94</v>
@@ -1317,7 +1341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1325,7 +1349,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -1337,7 +1361,7 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -1346,22 +1370,22 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <v>2.035</v>
+        <v>2.0350000000000001</v>
       </c>
       <c r="K8">
-        <v>1.055</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="L8">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="M8">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="N8">
-        <v>1.285</v>
+        <v>1.2849999999999999</v>
       </c>
       <c r="O8">
-        <v>3.115</v>
+        <v>3.1150000000000002</v>
       </c>
       <c r="P8">
         <v>2.915</v>
@@ -1370,7 +1394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1378,7 +1402,7 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -1390,7 +1414,7 @@
         <v>3</v>
       </c>
       <c r="G9">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="H9">
         <v>3</v>
@@ -1399,31 +1423,31 @@
         <v>3</v>
       </c>
       <c r="J9">
-        <v>2.055</v>
+        <v>2.0550000000000002</v>
       </c>
       <c r="K9">
-        <v>1.045</v>
+        <v>1.0449999999999999</v>
       </c>
       <c r="L9">
-        <v>1.245</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="M9">
         <v>1.105</v>
       </c>
       <c r="N9">
-        <v>1.215</v>
+        <v>1.2150000000000001</v>
       </c>
       <c r="O9">
         <v>2.94</v>
       </c>
       <c r="P9">
-        <v>2.985</v>
+        <v>2.9849999999999999</v>
       </c>
       <c r="Q9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1431,7 +1455,7 @@
         <v>2.625</v>
       </c>
       <c r="C10">
-        <v>2.735</v>
+        <v>2.7349999999999999</v>
       </c>
       <c r="D10">
         <v>3.15</v>
@@ -1440,7 +1464,7 @@
         <v>2.72</v>
       </c>
       <c r="F10">
-        <v>1.755</v>
+        <v>1.7549999999999999</v>
       </c>
       <c r="G10">
         <v>2.605</v>
@@ -1455,51 +1479,51 @@
         <v>1.5</v>
       </c>
       <c r="K10">
-        <v>3.155</v>
+        <v>3.1549999999999998</v>
       </c>
       <c r="L10">
         <v>1.345</v>
       </c>
       <c r="M10">
-        <v>1.305</v>
+        <v>1.3049999999999999</v>
       </c>
       <c r="N10">
-        <v>2.485</v>
+        <v>2.4849999999999999</v>
       </c>
       <c r="O10">
-        <v>2.845</v>
+        <v>2.8450000000000002</v>
       </c>
       <c r="P10">
-        <v>2.775</v>
+        <v>2.7749999999999999</v>
       </c>
       <c r="Q10">
-        <v>3.135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
+        <v>3.1349999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B11">
-        <v>2.985</v>
+        <v>2.9849999999999999</v>
       </c>
       <c r="C11">
-        <v>1.015</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="D11">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E11">
-        <v>3.255</v>
+        <v>3.2549999999999999</v>
       </c>
       <c r="F11">
         <v>1.36</v>
       </c>
       <c r="G11">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H11">
-        <v>1.005</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="I11">
         <v>1.17</v>
@@ -1511,10 +1535,10 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>2.235</v>
+        <v>2.2349999999999999</v>
       </c>
       <c r="M11">
-        <v>2.685</v>
+        <v>2.6850000000000001</v>
       </c>
       <c r="N11">
         <v>1.19</v>
@@ -1526,10 +1550,10 @@
         <v>2.86</v>
       </c>
       <c r="Q11">
-        <v>1.005</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+        <v>1.0049999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1543,7 +1567,7 @@
         <v>3.52</v>
       </c>
       <c r="E12">
-        <v>2.735</v>
+        <v>2.7349999999999999</v>
       </c>
       <c r="F12">
         <v>1.365</v>
@@ -1552,16 +1576,16 @@
         <v>1.54</v>
       </c>
       <c r="H12">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="I12">
-        <v>1.245</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="J12">
-        <v>1.445</v>
+        <v>1.4450000000000001</v>
       </c>
       <c r="K12">
-        <v>3.485</v>
+        <v>3.4849999999999999</v>
       </c>
       <c r="L12">
         <v>1.105</v>
@@ -1573,16 +1597,16 @@
         <v>1.34</v>
       </c>
       <c r="O12">
-        <v>2.595</v>
+        <v>2.5950000000000002</v>
       </c>
       <c r="P12">
         <v>2.41</v>
       </c>
       <c r="Q12">
-        <v>3.485</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
+        <v>3.4849999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -1590,22 +1614,22 @@
         <v>1.28</v>
       </c>
       <c r="C13">
-        <v>1.055</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="D13">
         <v>3.21</v>
       </c>
       <c r="E13">
-        <v>2.965</v>
+        <v>2.9649999999999999</v>
       </c>
       <c r="F13">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="G13">
-        <v>1.245</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="H13">
-        <v>1.025</v>
+        <v>1.0249999999999999</v>
       </c>
       <c r="I13">
         <v>1.105</v>
@@ -1614,13 +1638,13 @@
         <v>1.405</v>
       </c>
       <c r="K13">
-        <v>3.185</v>
+        <v>3.1850000000000001</v>
       </c>
       <c r="L13">
         <v>1.075</v>
       </c>
       <c r="M13">
-        <v>1.1825</v>
+        <v>1.1825000000000001</v>
       </c>
       <c r="N13">
         <v>1.37</v>
@@ -1629,13 +1653,13 @@
         <v>2.41</v>
       </c>
       <c r="P13">
-        <v>2.305</v>
+        <v>2.3050000000000002</v>
       </c>
       <c r="Q13">
         <v>3.105</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,13 +1667,13 @@
         <v>1.31</v>
       </c>
       <c r="C14">
-        <v>1.465</v>
+        <v>1.4650000000000001</v>
       </c>
       <c r="D14">
         <v>3.13</v>
       </c>
       <c r="E14">
-        <v>2.795</v>
+        <v>2.7949999999999999</v>
       </c>
       <c r="F14">
         <v>1.58</v>
@@ -1658,25 +1682,25 @@
         <v>1.79</v>
       </c>
       <c r="H14">
-        <v>1.185</v>
+        <v>1.1850000000000001</v>
       </c>
       <c r="I14">
         <v>1.165</v>
       </c>
       <c r="J14">
-        <v>3.135</v>
+        <v>3.1349999999999998</v>
       </c>
       <c r="K14">
         <v>1.04</v>
       </c>
       <c r="L14">
-        <v>1.315</v>
+        <v>1.3149999999999999</v>
       </c>
       <c r="M14">
         <v>1.27</v>
       </c>
       <c r="N14">
-        <v>1.3575</v>
+        <v>1.3574999999999999</v>
       </c>
       <c r="O14">
         <v>2.35</v>
@@ -1685,27 +1709,27 @@
         <v>2.21</v>
       </c>
       <c r="Q14">
-        <v>1.265</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
+        <v>1.2649999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B15">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="C15">
-        <v>1.775</v>
+        <v>1.7749999999999999</v>
       </c>
       <c r="D15">
-        <v>3.865</v>
+        <v>3.8650000000000002</v>
       </c>
       <c r="E15">
-        <v>2.635</v>
+        <v>2.6349999999999998</v>
       </c>
       <c r="F15">
-        <v>1.205</v>
+        <v>1.2050000000000001</v>
       </c>
       <c r="G15">
         <v>0.67</v>
@@ -1714,25 +1738,25 @@
         <v>0.49</v>
       </c>
       <c r="I15">
-        <v>0.665</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="J15">
         <v>0.995</v>
       </c>
       <c r="K15">
-        <v>3.935</v>
+        <v>3.9350000000000001</v>
       </c>
       <c r="L15">
-        <v>1.945</v>
+        <v>1.9450000000000001</v>
       </c>
       <c r="M15">
         <v>2.21</v>
       </c>
       <c r="N15">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="O15">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="P15">
         <v>2.36</v>
@@ -1741,7 +1765,7 @@
         <v>0.495</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -1749,19 +1773,19 @@
         <v>2.335</v>
       </c>
       <c r="C16">
-        <v>0.895</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="D16">
-        <v>3.825</v>
+        <v>3.8250000000000002</v>
       </c>
       <c r="E16">
         <v>2.665</v>
       </c>
       <c r="F16">
-        <v>1.255</v>
+        <v>1.2549999999999999</v>
       </c>
       <c r="G16">
-        <v>0.665</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="H16">
         <v>0.54</v>
@@ -1770,13 +1794,13 @@
         <v>0.66</v>
       </c>
       <c r="J16">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="K16">
-        <v>0.535</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="L16">
-        <v>1.735</v>
+        <v>1.7350000000000001</v>
       </c>
       <c r="M16">
         <v>2.105</v>
@@ -1788,13 +1812,13 @@
         <v>1.96</v>
       </c>
       <c r="P16">
-        <v>2.2825</v>
+        <v>2.2825000000000002</v>
       </c>
       <c r="Q16">
-        <v>0.555</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>0.55500000000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -1802,7 +1826,7 @@
         <v>3</v>
       </c>
       <c r="C17">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1814,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="G17">
-        <v>2.975</v>
+        <v>2.9750000000000001</v>
       </c>
       <c r="H17">
         <v>3</v>
@@ -1823,10 +1847,10 @@
         <v>3</v>
       </c>
       <c r="J17">
-        <v>2.735</v>
+        <v>2.7349999999999999</v>
       </c>
       <c r="K17">
-        <v>1.055</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="L17">
         <v>2.21</v>
@@ -1838,10 +1862,10 @@
         <v>1.34</v>
       </c>
       <c r="O17">
-        <v>3.095</v>
+        <v>3.0950000000000002</v>
       </c>
       <c r="P17">
-        <v>3.005</v>
+        <v>3.0049999999999999</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -1853,11 +1877,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1907,7 +1931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1960,7 +1984,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2013,7 +2037,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -2066,7 +2090,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -2119,7 +2143,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2172,7 +2196,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -2225,7 +2249,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -2278,7 +2302,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2331,7 +2355,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -2384,7 +2408,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -2437,7 +2461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2490,7 +2514,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -2543,7 +2567,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -2596,7 +2620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -2649,7 +2673,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,7 +2726,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -2761,11 +2785,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
@@ -2815,7 +2839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -2856,19 +2880,19 @@
         <v>0.1</v>
       </c>
       <c r="N2">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="O2">
         <v>0.54</v>
       </c>
       <c r="P2">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2897,13 +2921,13 @@
         <v>0.99</v>
       </c>
       <c r="J3">
-        <v>0.855</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="K3">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="L3">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M3">
         <v>0.02</v>
@@ -2921,7 +2945,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -2968,13 +2992,13 @@
         <v>0.97</v>
       </c>
       <c r="P4">
-        <v>0.975</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -3003,10 +3027,10 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>0.855</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="K5">
-        <v>0.5649999999999999</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="L5">
         <v>0.63</v>
@@ -3015,10 +3039,10 @@
         <v>0.88</v>
       </c>
       <c r="N5">
-        <v>0.6850000000000001</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="O5">
-        <v>0.605</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="P5">
         <v>0.61</v>
@@ -3027,7 +3051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3056,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="K6">
         <v>0.125</v>
@@ -3071,16 +3095,16 @@
         <v>0.22</v>
       </c>
       <c r="O6">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="P6">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -3112,13 +3136,13 @@
         <v>0.62</v>
       </c>
       <c r="K7">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="L7">
-        <v>0.265</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="M7">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="N7">
         <v>0.37</v>
@@ -3127,13 +3151,13 @@
         <v>0.05</v>
       </c>
       <c r="P7">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Q7">
         <v>0.99</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -3165,7 +3189,7 @@
         <v>0.255</v>
       </c>
       <c r="K8">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="L8">
         <v>0.155</v>
@@ -3177,16 +3201,16 @@
         <v>0.1</v>
       </c>
       <c r="O8">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P8">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -3227,7 +3251,7 @@
         <v>0.05</v>
       </c>
       <c r="N9">
-        <v>0.08500000000000001</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="O9">
         <v>0.05</v>
@@ -3239,7 +3263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -3250,19 +3274,19 @@
         <v>0.91</v>
       </c>
       <c r="D10">
-        <v>0.925</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="E10">
         <v>0.92</v>
       </c>
       <c r="F10">
-        <v>0.6850000000000001</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="G10">
         <v>0.625</v>
       </c>
       <c r="H10">
-        <v>0.385</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="I10">
         <v>0.39</v>
@@ -3271,28 +3295,28 @@
         <v>0.25</v>
       </c>
       <c r="K10">
-        <v>0.905</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="L10">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M10">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="N10">
-        <v>0.885</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="O10">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="P10">
         <v>0.115</v>
       </c>
       <c r="Q10">
-        <v>0.905</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
+        <v>0.90500000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -3300,13 +3324,13 @@
         <v>0.99</v>
       </c>
       <c r="C11">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="D11">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E11">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="F11">
         <v>0.11</v>
@@ -3315,10 +3339,10 @@
         <v>0.46</v>
       </c>
       <c r="H11">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="I11">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J11">
         <v>0.99</v>
@@ -3333,7 +3357,7 @@
         <v>0.99</v>
       </c>
       <c r="N11">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O11">
         <v>0.99</v>
@@ -3342,24 +3366,24 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B12">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="C12">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="D12">
         <v>0.74</v>
       </c>
       <c r="E12">
-        <v>0.485</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="F12">
         <v>0.12</v>
@@ -3380,7 +3404,7 @@
         <v>0.74</v>
       </c>
       <c r="L12">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="M12">
         <v>0.03</v>
@@ -3398,27 +3422,27 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B13">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="C13">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D13">
-        <v>0.895</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="E13">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="F13">
         <v>0.08</v>
       </c>
       <c r="G13">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="H13">
         <v>0.01</v>
@@ -3427,16 +3451,16 @@
         <v>0.05</v>
       </c>
       <c r="J13">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="K13">
         <v>0.89</v>
       </c>
       <c r="L13">
-        <v>0.025</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="M13">
-        <v>0.075</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="N13">
         <v>0.125</v>
@@ -3445,13 +3469,13 @@
         <v>0.51</v>
       </c>
       <c r="P13">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="Q13">
         <v>0.92</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3462,34 +3486,34 @@
         <v>0.22</v>
       </c>
       <c r="D14">
-        <v>0.9350000000000001</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="E14">
-        <v>0.555</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="F14">
         <v>0.17</v>
       </c>
       <c r="G14">
-        <v>0.365</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H14">
         <v>0.12</v>
       </c>
       <c r="I14">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="J14">
         <v>0.755</v>
       </c>
       <c r="K14">
-        <v>0.055</v>
+        <v>5.5E-2</v>
       </c>
       <c r="L14">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="M14">
-        <v>0.145</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="N14">
         <v>0.155</v>
@@ -3498,24 +3522,24 @@
         <v>0.44</v>
       </c>
       <c r="P14">
-        <v>0.345</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="Q14">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B15">
-        <v>0.535</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="C15">
-        <v>0.555</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="D15">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="E15">
         <v>0.505</v>
@@ -3533,16 +3557,16 @@
         <v>0.505</v>
       </c>
       <c r="J15">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="K15">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="L15">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M15">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="N15">
         <v>0.5</v>
@@ -3554,10 +3578,10 @@
         <v>0.41</v>
       </c>
       <c r="Q15">
-        <v>0.525</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -3565,7 +3589,7 @@
         <v>0.54</v>
       </c>
       <c r="C16">
-        <v>0.555</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="D16">
         <v>0.54</v>
@@ -3583,34 +3607,34 @@
         <v>0.48</v>
       </c>
       <c r="I16">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="J16">
-        <v>0.485</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="K16">
-        <v>0.465</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="L16">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="M16">
-        <v>0.485</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="N16">
-        <v>0.425</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="O16">
         <v>0.49</v>
       </c>
       <c r="P16">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="Q16">
         <v>0.51</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
@@ -3639,22 +3663,22 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>0.985</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="K17">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="L17">
-        <v>0.985</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="M17">
-        <v>0.985</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="N17">
         <v>0.125</v>
       </c>
       <c r="O17">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P17">
         <v>0.02</v>
